--- a/Projetos/Lojas Conamore/Relatórios Pagar.me/ACL/Pagarme_ACL_2026-06-19_21.xlsx
+++ b/Projetos/Lojas Conamore/Relatórios Pagar.me/ACL/Pagarme_ACL_2026-06-19_21.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Revisar" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Aprovados'!$A$1:$G$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Revisar'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Aprovados'!$A$1:$L$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Revisar'!$A$1:$L$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,7 +61,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,2055 +429,3243 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>loja</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>cliente</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pedido</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>referência</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>aprovado_em</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>flag</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>NSU</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Customer_Email</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction_Id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Meguiane  Arruda</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>PM9FRDIY57</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>PM9FRDIY57</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>R$ 339,88</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-06-19 00:27:10 -03</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 00:27:10 -03:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4444298196</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4444298196</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>meggomesarruda@gmail.com</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>tran_nwBk3x3Sph374RdA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>JULIA LINHARES</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>ERVRBKZIW1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>ERVRBKZIW1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>R$ 913,20</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-19 02:09:30 -03</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 02:09:30 -03:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4444338237</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4444338237</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>juliaclinhares@yahoo.com.br</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>tran_lyAvn4GH4TejKLjW</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Lara Império</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>837FLDI7O6</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>44000002474</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>R$ 279,39</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>boleto</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-06-19 08:23:37 -03</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 08:23:37 -03:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>laraimperio28@gmail.com</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>tran_NzPWYZnfjhOY07Xx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>TATIELLY GARCEZ REVOREDO MARQUES</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>EL8ZH9HGDP</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>11000029912</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>R$ 753,78</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-06-19 09:28:17 -03</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 09:28:17 -03:00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>tatiellyrevoredo@gmail.com</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>tran_2vBrVyrauBTv0xq6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Andréa Hilário</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>3D2U0DI1N3</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>3D2U0DI1N3</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>R$ 129,75</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-19 09:40:58 -03</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 09:40:58 -03:00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4444555290</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4444555290</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>andrea.hilario40@gmail.com</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>tran_9rB0Q3pFAnc6kx5D</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Felipe Moyses</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>QZ5U7DCVVW</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>QZ5U7DCVVW</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>R$ 977,40</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-06-19 09:50:32 -03</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 09:50:32 -03:00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4444567231</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4444567231</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>luanrsilva@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>tran_2PV4QNqSRKsmXd7D</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Tatiana Fonseca</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>PKKWH31CKP</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>PKKWH31CKP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>R$ 962,16</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-19 10:54:02 -03</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 10:54:02 -03:00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4444644503</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4444644503</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>tatiff21@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>tran_X7kK55Gie8cbKm5J</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Lucas Abrantes</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>7E2JTR1CQL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>7E2JTR1CQL</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>R$ 697,00</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-19 11:01:20 -03</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 11:01:20 -03:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4444653357</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4444653357</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>lucasthads@gmail.com</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>tran_Yk1waWmSxrs7y0oM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Suelen Garcia Bastos</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>RW2KHEGF94</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>11000029917</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>R$ 734,38</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-19 11:44:25 -03</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 11:44:25 -03:00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>suelen.bastos@sjp.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>tran_nP1907asbUve3LBp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>marice conde</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0K2XAVBR7Y</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>0K2XAVBR7Y</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>R$ 731,20</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-19 11:45:44 -03</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 11:45:44 -03:00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4444707109</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4444707109</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>mariceconde@gmail.com</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>tran_P8yX4Vwi1H7Pj9vN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Gabriela Koehler Carvalho</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>W4NC46BLK2</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>W4NC46BLK2</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>R$ 342,20</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-19 12:34:12 -03</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 12:34:12 -03:00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4444766990</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4444766990</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>gabickoehler@gmail.com</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>tran_8M4el9Mf0U5VrqAb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>erica moreira</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>7YOJSVRI8X</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>11000029920</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>R$ 490,50</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-19 12:35:40 -03</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>2026-06-19 12:35:40 -03:00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>dond.22@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>tran_znR5KbwBs8CkZb8k</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>erica moreira</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>J0O2S1PALK</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>11000029921</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>R$ 381,12</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-19 12:52:51 -03</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>2026-06-19 12:52:51 -03:00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>dond.22@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>tran_jgQWbmwGcyhwqLPO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Nathalia Ricardo</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>E2OPS0AG0M</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>E2OPS0AG0M</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>R$ 283,56</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-19 13:29:00 -03</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 13:29:00 -03:00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4444833010</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4444833010</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>nathalia.ricardo@live.com</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>tran_Omyw7Jxhvso3QJj0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>MAYRA HONORATO</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>VZ5OCGTK8E</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>44000002480</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>R$ 230,66</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-19 15:12:23 -03</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 15:12:23 -03:00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>honoratoc.mayra@gmail.com</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>tran_MY9Jey9hryUpxJgW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>JULIANA TEIXEIRA BOMBIG</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>09RGUGEHVG</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>09RGUGEHVG</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>R$ 372,10</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-19 15:56:43 -03</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 15:56:43 -03:00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4445009326</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4445009326</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>julianabombig@gmail.com</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>tran_adM9pWVspfKkeAOr</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Rodrigo de Moura Lavoura</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>R9DMFLZTYZ</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>R9DMFLZTYZ</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>R$ 530,15</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-19 15:58:54 -03</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 15:58:54 -03:00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4445011850</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4445011850</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>bmoura975@gmail.com</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>tran_vpkb5NCJBUllMWqm</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Sandra Schnyder</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>PYQ9B21TM6</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>11000029924</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>R$ 598,30</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-19 16:19:36 -03</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 16:19:36 -03:00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>nenisdomosi@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>tran_EZzXdmeSrUbDJ2r8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Adrienne Viti</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>K19RTXIGW3</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>11000029925</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>R$ 251,33</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-19 16:51:12 -03</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 16:51:12 -03:00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adrienneviti@gmail.com</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>tran_DKbV8drTkJIRVJmM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Milene Dumont</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>XWZ5A7YI97</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>44000002482</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>R$ 154,67</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-06-19 17:19:35 -03</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 17:19:35 -03:00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>mi.dumont2009@gmail.com</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>tran_MADx3L2i2MIDLb0g</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>SEBASTIÃO GERALDO DA SILVA BRITO</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>P9LDTYNAKJ</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>11000029926</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>R$ 511,70</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-19 17:31:50 -03</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 17:31:50 -03:00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>shoah7779@gmail.com</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>tran_aKZrzPO0uyIXWGJV</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>Loana Maria de Siqueira</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>7K05XSDS4P</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>7K05XSDS4P</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>R$ 1.172,00</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-19 21:05:57 -03</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 21:05:57 -03:00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4445470737</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>4445470737</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>lomasiq@gmail.com</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>tran_xEabz9VIGduX6r39</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Alessandra Moura</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>QM6OSL4B2Z</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>QM6OSL4B2Z</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>R$ 585,48</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-06-19 22:39:22 -03</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-19 22:39:22 -03:00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4445562066</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>4445562066</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>dellep24@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>tran_MQrzq7RtOYSxYDdj</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Berenice Nunes</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>6M4GWU5SQ8</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>6M4GWU5SQ8</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>R$ 395,60</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-06-20 08:46:19 -03</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 08:46:19 -03:00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4445821974</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>4445821974</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>bere_martez@outlook.com</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>tran_e360g0kHmMi3R7qx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Deborah Maeda</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>04E3CWF928</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>04E3CWF928</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>R$ 157,51</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-06-20 09:10:06 -03</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 09:10:06 -03:00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4445844291</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>4445844291</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>dehfunchal@gmail.com</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>tran_m3wMJDJCeeh08Wob</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>Angelina Villani Passarella</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>5O51TYJTEW</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>11000029931</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>R$ 176,33</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-20 09:27:42 -03</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 09:27:42 -03:00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>apassarella@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>tran_y9W2MeDI5s6r0eqQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>VANUSA Nascimento de melo</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>8XZ9TY1ULP</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>44000002483</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>R$ 224,20</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-20 11:19:55 -03</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 11:19:55 -03:00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vanusa1melo@gmail.com</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>tran_wyg51p8IMf1KdoaX</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Eridan Roberto de Santana</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>EL1MHJMIVW</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>44000002484</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>R$ 262,86</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-20 13:22:23 -03</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 13:22:23 -03:00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>eridanrobertos@gmail.com</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>tran_BYy9MXt7VfvBjZ4Q</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Davidson Pereira de Souza Afonso Pinto</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>40Z5AKGAJ4</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>11000029932</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>R$ 338,88</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-20 14:05:39 -03</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 14:05:39 -03:00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>filhodedavi.ms@gmail.com</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>tran_Dyg68Q5FGvHVXPQA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Ana Ponchon</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>6O8OA12SRK</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>6O8OA12SRK</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>R$ 511,18</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-20 14:44:48 -03</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 14:44:48 -03:00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4446212119</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>4446212119</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>acponchon@gmail.com</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>tran_m0PZbq1U4S0gb1yp</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>José  Cavalcante Júnior</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>91DYC2WTX5</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>11000029935</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>R$ 344,44</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-20 15:17:26 -03</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 15:17:26 -03:00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>cavalcantejuniorpi@yahoo.com.br</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>tran_7r9objAcW5hjwodZ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Alessandra  Semm</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>P9QSX5H85P</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>11000029936</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>R$ 174,49</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-20 15:31:11 -03</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 15:31:11 -03:00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>portelalessandra@gmail.com</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>tran_yrv3PNZc5mt4bKNq</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Luiza Crochemore</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>N909HY6B8G</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>11000029938</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>R$ 1.136,06</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-20 16:17:28 -03</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 16:17:28 -03:00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>crochemorelu@gmail.com</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>tran_nkRE7ADUyhmY3rJY</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Andre Vinicius lino Silva  Pinto</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>XJJRAZJU06</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>11000029940</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>R$ 264,52</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-06-20 16:56:43 -03</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 16:56:43 -03:00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>andrepinto@indanet.com.br</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>tran_OP9QzkuEYcjRgVDw</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Liane Henriques Fraccaroli</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>P69QB6CEKP</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>P69QB6CEKP</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>R$ 1.457,40</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-20 17:01:55 -03</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 17:01:55 -03:00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4446359095</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>4446359095</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>liane@o2filmes.com</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>tran_PqQKq30uyHVlDnZR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>Ananda  Lima</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>LK17C24U2E</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>LK17C24U2E</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>R$ 1.546,30</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-20 17:05:07 -03</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 17:05:07 -03:00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4446362528</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4446362528</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>doutoraanandalima@gmail.com</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>tran_ZaQrp6lhv7Sp9BzJ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Thiago Sayão</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>6KNOC9KBE6</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>11000029943</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>R$ 430,86</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-20 17:36:32 -03</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 17:36:32 -03:00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>thiago.sayao@gmail.com</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>tran_WRJqbYAseYTwLpmE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>Paulo Nogueira</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Q6O1I1LU95</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Q6O1I1LU95</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>R$ 313,40</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-20 18:55:28 -03</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 18:55:28 -03:00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4446498606</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4446498606</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>paulo.victorsn@gmail.com</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>tran_0djM7JxSrSaAOREm</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Thatiane Nunes</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>JD1ZIZIY3P</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>JD1ZIZIY3P</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>R$ 408,50</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-20 21:23:22 -03</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 21:23:22 -03:00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4446664204</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4446664204</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>thatiane.nunes.pereira@gmail.com</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>tran_jb9LMxBIdJIEBGXp</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Eliane Higa</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>L5EDB6HY5G</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>L5EDB6HY5G</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>R$ 148,22</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-20 22:29:35 -03</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-20 22:29:35 -03:00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4446721086</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4446721086</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>elianehiga@gmail.com</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>tran_LX7zjRb7fGs6jnA6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>Marilia Fontes</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>DJ7R7AXFOJ</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>DJ7R7AXFOJ</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>R$ 1.093,61</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-06-21 11:00:59 -03</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 11:00:59 -03:00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4447114682</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4447114682</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>mariliadfontes@gmail.com</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>tran_3DYzvrgTWMtvzmKp</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Helena Avzaradel</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>RL9VAK7IX2</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>RL9VAK7IX2</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>R$ 520,50</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-06-21 13:17:42 -03</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 13:17:42 -03:00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4447281406</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4447281406</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>helena.avzaradel@gmail.com</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>tran_6Wdb1aDUds4Pq7gA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Benedito mauro dos santos</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>7YZFPRT34O</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>7YZFPRT34O</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>R$ 90,21</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-21 14:33:54 -03</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 14:33:54 -03:00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4447374889</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4447374889</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>gisa.fernanda@terra.com.br</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>tran_Y293VmxEC2TvJvjQ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Rodrigo Santana</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>PJJ1H30AX1</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>11000029951</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>R$ 231,55</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-06-21 15:07:22 -03</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 15:07:22 -03:00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Rodrigo.santana12345@outlook.com</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>tran_xrMA8OS2BIZ5jz4G</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>Marcia  Posman</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>MZV2IP3IZO</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>MZV2IP3IZO</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>R$ 169,98</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-06-21 15:07:56 -03</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 15:07:56 -03:00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4447415412</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4447415412</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>marcia.posman@uol.com.br</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>tran_LDkpjMGS9bf9rEYR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Roselanhe Oliveira</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>1Q4JTPUMKV</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>1Q4JTPUMKV</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>R$ 894,34</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-06-21 16:57:29 -03</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 16:57:29 -03:00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4447538965</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>4447538965</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>roselanhe@yahoo.com.br</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>tran_E75Pe6AAfdhPLlR0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Vanessa Mekaru</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>KOG6SZGH1W</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>KOG6SZGH1W</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>R$ 1.297,95</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-06-21 17:59:44 -03</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 17:59:44 -03:00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4447611652</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>4447611652</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>van_mek@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>tran_mvwd0NATWcDGylXp</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Diego   dos Santos</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2PWANKAOY4</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2PWANKAOY4</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>R$ 223,40</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-06-21 18:40:56 -03</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 18:40:56 -03:00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4447669667</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>4447669667</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>delainesoares@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>tran_VB4O8E6h8wu0bday</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>Marcio Kataoka</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>43Z51B6SKL</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>11000029955</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>R$ 100,28</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-06-21 18:49:58 -03</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 18:49:58 -03:00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>mkataoka@gmail.com</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>tran_NyqzrPGlCdcvoaY8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>Erich Augusto  Grunevald</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>9MN6C1VB3K</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>11000029956</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>R$ 408,91</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-06-21 18:51:15 -03</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 18:51:15 -03:00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>erich.augusto@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>tran_8KrpV5NFEVHrDzwy</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Vanessa Schroeder</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>JNW1UPNHV3</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>JNW1UPNHV3</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>R$ 414,78</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-06-21 19:11:00 -03</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 19:11:00 -03:00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4447712040</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>4447712040</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>nessaaah_@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>tran_gDMmDJSMZSa292XL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Felipe Guimarães Figueiredo de Oliveira Motta</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>L41SWYTQ1L</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>11000029958</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>R$ 667,31</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-06-21 19:31:01 -03</t>
-        </is>
-      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 19:31:01 -03:00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>felipeguimaraesusa@gmail.com</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>tran_vOMzmJ8ibwS6xYl3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>Campolina Diniz investimentos ltda</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>6Q32T8QIE1</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>11000029959</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>R$ 386,11</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-06-21 19:33:29 -03</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 19:33:29 -03:00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adrianamdvb@gmail.com</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>tran_Y0QK62AdTwHkj72l</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Suelem Larissa  Fruzeri Desiro</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>LOVYU9YT1Q</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>LOVYU9YT1Q</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>R$ 271,60</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-21 21:02:10 -03</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>2026-06-21 21:02:10 -03:00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4447841994</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4447841994</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>sufruzeri@gmail.com</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>tran_VDY8G8PsmHvlGkg3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G55"/>
+  <autoFilter ref="A1:L55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2486,131 +3676,195 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>loja</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>cliente</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pedido</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>referência</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>aprovado_em</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>flag</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>NSU</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Customer_Email</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction_Id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>erica moreira</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>7YOJSVRI8X</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>11000029920</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>R$ 490,50</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-06-19 12:35:40 -03</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>2026-06-19 12:35:40 -03:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>dond.22@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>tran_znR5KbwBs8CkZb8k</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>erica moreira</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>J0O2S1PALK</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>11000029921</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>R$ 381,12</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-19 12:52:51 -03</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>2026-06-19 12:52:51 -03:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>REVISAR</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>dond.22@hotmail.com</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>tran_jgQWbmwGcyhwqLPO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:L3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Projetos/Lojas Conamore/Relatórios Pagar.me/ACL/Pagarme_ACL_2026-06-19_21.xlsx
+++ b/Projetos/Lojas Conamore/Relatórios Pagar.me/ACL/Pagarme_ACL_2026-06-19_21.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Revisar" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Aprovados'!$A$1:$L$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Aprovados'!$A$1:$L$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Revisar'!$A$1:$L$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59,11 +59,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -439,11 +440,11 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,27 +485,27 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>NSU</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TID</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Customer_Email</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction_Id</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>flag</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>NSU</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TID</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Customer_Email</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transaction_Id</t>
         </is>
       </c>
     </row>
@@ -529,10 +530,8 @@
           <t>PM9FRDIY57</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>R$ 339,88</t>
-        </is>
+      <c r="E2" s="2" t="n">
+        <v>339.88</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -546,7 +545,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4444298196</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -556,17 +555,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4444298196</t>
+          <t>meggomesarruda@gmail.com</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>meggomesarruda@gmail.com</t>
+          <t>tran_nwBk3x3Sph374RdA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>tran_nwBk3x3Sph374RdA</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -591,10 +590,8 @@
           <t>ERVRBKZIW1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>R$ 913,20</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>913.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -608,7 +605,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4444338237</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -618,17 +615,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4444338237</t>
+          <t>juliaclinhares@yahoo.com.br</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>juliaclinhares@yahoo.com.br</t>
+          <t>tran_lyAvn4GH4TejKLjW</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>tran_lyAvn4GH4TejKLjW</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -653,10 +650,8 @@
           <t>44000002474</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>R$ 279,39</t>
-        </is>
+      <c r="E4" s="2" t="n">
+        <v>279.39</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -668,21 +663,21 @@
           <t>2026-06-19 08:23:37 -03:00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>laraimperio28@gmail.com</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>laraimperio28@gmail.com</t>
+          <t>tran_NzPWYZnfjhOY07Xx</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>tran_NzPWYZnfjhOY07Xx</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -707,10 +702,8 @@
           <t>11000029912</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>R$ 753,78</t>
-        </is>
+      <c r="E5" s="2" t="n">
+        <v>753.78</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,21 +715,21 @@
           <t>2026-06-19 09:28:17 -03:00</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>tatiellyrevoredo@gmail.com</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>tatiellyrevoredo@gmail.com</t>
+          <t>tran_2vBrVyrauBTv0xq6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>tran_2vBrVyrauBTv0xq6</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -761,10 +754,8 @@
           <t>3D2U0DI1N3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>R$ 129,75</t>
-        </is>
+      <c r="E6" s="2" t="n">
+        <v>129.75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -778,7 +769,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4444555290</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -788,17 +779,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4444555290</t>
+          <t>andrea.hilario40@gmail.com</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>andrea.hilario40@gmail.com</t>
+          <t>tran_9rB0Q3pFAnc6kx5D</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>tran_9rB0Q3pFAnc6kx5D</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -823,10 +814,8 @@
           <t>QZ5U7DCVVW</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>R$ 977,40</t>
-        </is>
+      <c r="E7" s="2" t="n">
+        <v>977.4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -840,7 +829,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4444567231</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -850,17 +839,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4444567231</t>
+          <t>luanrsilva@hotmail.com</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>luanrsilva@hotmail.com</t>
+          <t>tran_2PV4QNqSRKsmXd7D</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>tran_2PV4QNqSRKsmXd7D</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -885,10 +874,8 @@
           <t>PKKWH31CKP</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>R$ 962,16</t>
-        </is>
+      <c r="E8" s="2" t="n">
+        <v>962.16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -902,7 +889,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4444644503</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -912,17 +899,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4444644503</t>
+          <t>tatiff21@hotmail.com</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>tatiff21@hotmail.com</t>
+          <t>tran_X7kK55Gie8cbKm5J</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>tran_X7kK55Gie8cbKm5J</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -947,10 +934,8 @@
           <t>7E2JTR1CQL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>R$ 697,00</t>
-        </is>
+      <c r="E9" s="2" t="n">
+        <v>697</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -964,7 +949,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4444653357</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -974,17 +959,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4444653357</t>
+          <t>lucasthads@gmail.com</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>lucasthads@gmail.com</t>
+          <t>tran_Yk1waWmSxrs7y0oM</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>tran_Yk1waWmSxrs7y0oM</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1009,10 +994,8 @@
           <t>11000029917</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>R$ 734,38</t>
-        </is>
+      <c r="E10" s="2" t="n">
+        <v>734.38</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1024,21 +1007,21 @@
           <t>2026-06-19 11:44:25 -03:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>suelen.bastos@sjp.pr.gov.br</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suelen.bastos@sjp.pr.gov.br</t>
+          <t>tran_nP1907asbUve3LBp</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>tran_nP1907asbUve3LBp</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1063,10 +1046,8 @@
           <t>0K2XAVBR7Y</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>R$ 731,20</t>
-        </is>
+      <c r="E11" s="2" t="n">
+        <v>731.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1080,7 +1061,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4444707109</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1090,17 +1071,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4444707109</t>
+          <t>mariceconde@gmail.com</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>mariceconde@gmail.com</t>
+          <t>tran_P8yX4Vwi1H7Pj9vN</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>tran_P8yX4Vwi1H7Pj9vN</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1125,10 +1106,8 @@
           <t>W4NC46BLK2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>R$ 342,20</t>
-        </is>
+      <c r="E12" s="2" t="n">
+        <v>342.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1142,7 +1121,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4444766990</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1152,17 +1131,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4444766990</t>
+          <t>gabickoehler@gmail.com</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>gabickoehler@gmail.com</t>
+          <t>tran_8M4el9Mf0U5VrqAb</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>tran_8M4el9Mf0U5VrqAb</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1187,10 +1166,8 @@
           <t>11000029920</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>R$ 490,50</t>
-        </is>
+      <c r="E13" s="2" t="n">
+        <v>490.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1202,21 +1179,21 @@
           <t>2026-06-19 12:35:40 -03:00</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dond.22@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>tran_znR5KbwBs8CkZb8k</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>dond.22@hotmail.com</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>tran_znR5KbwBs8CkZb8k</t>
         </is>
       </c>
     </row>
@@ -1241,10 +1218,8 @@
           <t>11000029921</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>R$ 381,12</t>
-        </is>
+      <c r="E14" s="2" t="n">
+        <v>381.12</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1256,21 +1231,21 @@
           <t>2026-06-19 12:52:51 -03:00</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dond.22@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>tran_jgQWbmwGcyhwqLPO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>dond.22@hotmail.com</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>tran_jgQWbmwGcyhwqLPO</t>
         </is>
       </c>
     </row>
@@ -1295,10 +1270,8 @@
           <t>E2OPS0AG0M</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>R$ 283,56</t>
-        </is>
+      <c r="E15" s="2" t="n">
+        <v>283.56</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1312,7 +1285,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4444833010</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1322,17 +1295,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4444833010</t>
+          <t>nathalia.ricardo@live.com</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>nathalia.ricardo@live.com</t>
+          <t>tran_Omyw7Jxhvso3QJj0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>tran_Omyw7Jxhvso3QJj0</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1357,10 +1330,8 @@
           <t>44000002480</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>R$ 230,66</t>
-        </is>
+      <c r="E16" s="2" t="n">
+        <v>230.66</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1372,21 +1343,21 @@
           <t>2026-06-19 15:12:23 -03:00</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>honoratoc.mayra@gmail.com</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>honoratoc.mayra@gmail.com</t>
+          <t>tran_MY9Jey9hryUpxJgW</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>tran_MY9Jey9hryUpxJgW</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1411,10 +1382,8 @@
           <t>09RGUGEHVG</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>R$ 372,10</t>
-        </is>
+      <c r="E17" s="2" t="n">
+        <v>372.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1428,7 +1397,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4445009326</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1438,17 +1407,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4445009326</t>
+          <t>julianabombig@gmail.com</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>julianabombig@gmail.com</t>
+          <t>tran_adM9pWVspfKkeAOr</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>tran_adM9pWVspfKkeAOr</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1473,10 +1442,8 @@
           <t>R9DMFLZTYZ</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>R$ 530,15</t>
-        </is>
+      <c r="E18" s="2" t="n">
+        <v>530.15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1490,7 +1457,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4445011850</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1500,17 +1467,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4445011850</t>
+          <t>bmoura975@gmail.com</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>bmoura975@gmail.com</t>
+          <t>tran_vpkb5NCJBUllMWqm</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>tran_vpkb5NCJBUllMWqm</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1535,10 +1502,8 @@
           <t>11000029924</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>R$ 598,30</t>
-        </is>
+      <c r="E19" s="2" t="n">
+        <v>598.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1550,21 +1515,21 @@
           <t>2026-06-19 16:19:36 -03:00</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>nenisdomosi@hotmail.com</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>nenisdomosi@hotmail.com</t>
+          <t>tran_EZzXdmeSrUbDJ2r8</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>tran_EZzXdmeSrUbDJ2r8</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1589,10 +1554,8 @@
           <t>11000029925</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>R$ 251,33</t>
-        </is>
+      <c r="E20" s="2" t="n">
+        <v>251.33</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1604,21 +1567,21 @@
           <t>2026-06-19 16:51:12 -03:00</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>adrienneviti@gmail.com</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>adrienneviti@gmail.com</t>
+          <t>tran_DKbV8drTkJIRVJmM</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>tran_DKbV8drTkJIRVJmM</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1643,10 +1606,8 @@
           <t>44000002482</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>R$ 154,67</t>
-        </is>
+      <c r="E21" s="2" t="n">
+        <v>154.67</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1658,21 +1619,21 @@
           <t>2026-06-19 17:19:35 -03:00</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mi.dumont2009@gmail.com</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>mi.dumont2009@gmail.com</t>
+          <t>tran_MADx3L2i2MIDLb0g</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>tran_MADx3L2i2MIDLb0g</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1697,10 +1658,8 @@
           <t>11000029926</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>R$ 511,70</t>
-        </is>
+      <c r="E22" s="2" t="n">
+        <v>511.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1712,21 +1671,21 @@
           <t>2026-06-19 17:31:50 -03:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>shoah7779@gmail.com</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>shoah7779@gmail.com</t>
+          <t>tran_aKZrzPO0uyIXWGJV</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>tran_aKZrzPO0uyIXWGJV</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1751,10 +1710,8 @@
           <t>7K05XSDS4P</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>R$ 1.172,00</t>
-        </is>
+      <c r="E23" s="2" t="n">
+        <v>1172</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1768,7 +1725,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4445470737</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1778,17 +1735,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4445470737</t>
+          <t>lomasiq@gmail.com</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>lomasiq@gmail.com</t>
+          <t>tran_xEabz9VIGduX6r39</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>tran_xEabz9VIGduX6r39</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1813,10 +1770,8 @@
           <t>QM6OSL4B2Z</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>R$ 585,48</t>
-        </is>
+      <c r="E24" s="2" t="n">
+        <v>585.48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1830,7 +1785,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4445562066</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1840,17 +1795,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4445562066</t>
+          <t>dellep24@hotmail.com</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>dellep24@hotmail.com</t>
+          <t>tran_MQrzq7RtOYSxYDdj</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>tran_MQrzq7RtOYSxYDdj</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1875,10 +1830,8 @@
           <t>6M4GWU5SQ8</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>R$ 395,60</t>
-        </is>
+      <c r="E25" s="2" t="n">
+        <v>395.6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1892,7 +1845,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4445821974</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1902,17 +1855,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4445821974</t>
+          <t>bere_martez@outlook.com</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>bere_martez@outlook.com</t>
+          <t>tran_e360g0kHmMi3R7qx</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>tran_e360g0kHmMi3R7qx</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1937,10 +1890,8 @@
           <t>04E3CWF928</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>R$ 157,51</t>
-        </is>
+      <c r="E26" s="2" t="n">
+        <v>157.51</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1954,7 +1905,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4445844291</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1964,17 +1915,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4445844291</t>
+          <t>dehfunchal@gmail.com</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>dehfunchal@gmail.com</t>
+          <t>tran_m3wMJDJCeeh08Wob</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>tran_m3wMJDJCeeh08Wob</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1999,10 +1950,8 @@
           <t>11000029931</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>R$ 176,33</t>
-        </is>
+      <c r="E27" s="2" t="n">
+        <v>176.33</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2014,21 +1963,21 @@
           <t>2026-06-20 09:27:42 -03:00</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>apassarella@hotmail.com</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>apassarella@hotmail.com</t>
+          <t>tran_y9W2MeDI5s6r0eqQ</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>tran_y9W2MeDI5s6r0eqQ</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2053,10 +2002,8 @@
           <t>44000002483</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>R$ 224,20</t>
-        </is>
+      <c r="E28" s="2" t="n">
+        <v>224.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2068,21 +2015,21 @@
           <t>2026-06-20 11:19:55 -03:00</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>vanusa1melo@gmail.com</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>vanusa1melo@gmail.com</t>
+          <t>tran_wyg51p8IMf1KdoaX</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>tran_wyg51p8IMf1KdoaX</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2107,10 +2054,8 @@
           <t>44000002484</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>R$ 262,86</t>
-        </is>
+      <c r="E29" s="2" t="n">
+        <v>262.86</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2122,21 +2067,21 @@
           <t>2026-06-20 13:22:23 -03:00</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>eridanrobertos@gmail.com</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>eridanrobertos@gmail.com</t>
+          <t>tran_BYy9MXt7VfvBjZ4Q</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>tran_BYy9MXt7VfvBjZ4Q</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2161,10 +2106,8 @@
           <t>11000029932</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>R$ 338,88</t>
-        </is>
+      <c r="E30" s="2" t="n">
+        <v>338.88</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2176,21 +2119,21 @@
           <t>2026-06-20 14:05:39 -03:00</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>filhodedavi.ms@gmail.com</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>filhodedavi.ms@gmail.com</t>
+          <t>tran_Dyg68Q5FGvHVXPQA</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>tran_Dyg68Q5FGvHVXPQA</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2215,10 +2158,8 @@
           <t>6O8OA12SRK</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>R$ 511,18</t>
-        </is>
+      <c r="E31" s="2" t="n">
+        <v>511.18</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2232,7 +2173,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4446212119</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2242,17 +2183,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4446212119</t>
+          <t>acponchon@gmail.com</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>acponchon@gmail.com</t>
+          <t>tran_m0PZbq1U4S0gb1yp</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>tran_m0PZbq1U4S0gb1yp</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2277,10 +2218,8 @@
           <t>11000029935</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>R$ 344,44</t>
-        </is>
+      <c r="E32" s="2" t="n">
+        <v>344.44</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2292,21 +2231,21 @@
           <t>2026-06-20 15:17:26 -03:00</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>cavalcantejuniorpi@yahoo.com.br</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>cavalcantejuniorpi@yahoo.com.br</t>
+          <t>tran_7r9objAcW5hjwodZ</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>tran_7r9objAcW5hjwodZ</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2331,10 +2270,8 @@
           <t>11000029936</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>R$ 174,49</t>
-        </is>
+      <c r="E33" s="2" t="n">
+        <v>174.49</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2346,21 +2283,21 @@
           <t>2026-06-20 15:31:11 -03:00</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>portelalessandra@gmail.com</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>portelalessandra@gmail.com</t>
+          <t>tran_yrv3PNZc5mt4bKNq</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>tran_yrv3PNZc5mt4bKNq</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2385,10 +2322,8 @@
           <t>11000029938</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>R$ 1.136,06</t>
-        </is>
+      <c r="E34" s="2" t="n">
+        <v>1136.06</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2400,21 +2335,21 @@
           <t>2026-06-20 16:17:28 -03:00</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>crochemorelu@gmail.com</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>crochemorelu@gmail.com</t>
+          <t>tran_nkRE7ADUyhmY3rJY</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>tran_nkRE7ADUyhmY3rJY</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2439,10 +2374,8 @@
           <t>11000029940</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>R$ 264,52</t>
-        </is>
+      <c r="E35" s="2" t="n">
+        <v>264.52</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2454,21 +2387,21 @@
           <t>2026-06-20 16:56:43 -03:00</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>andrepinto@indanet.com.br</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>andrepinto@indanet.com.br</t>
+          <t>tran_OP9QzkuEYcjRgVDw</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>tran_OP9QzkuEYcjRgVDw</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2493,10 +2426,8 @@
           <t>P69QB6CEKP</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>R$ 1.457,40</t>
-        </is>
+      <c r="E36" s="2" t="n">
+        <v>1457.4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2510,7 +2441,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4446359095</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2520,17 +2451,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4446359095</t>
+          <t>liane@o2filmes.com</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>liane@o2filmes.com</t>
+          <t>tran_PqQKq30uyHVlDnZR</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>tran_PqQKq30uyHVlDnZR</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2555,10 +2486,8 @@
           <t>LK17C24U2E</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>R$ 1.546,30</t>
-        </is>
+      <c r="E37" s="2" t="n">
+        <v>1546.3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2572,7 +2501,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4446362528</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2582,17 +2511,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4446362528</t>
+          <t>doutoraanandalima@gmail.com</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>doutoraanandalima@gmail.com</t>
+          <t>tran_ZaQrp6lhv7Sp9BzJ</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>tran_ZaQrp6lhv7Sp9BzJ</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2617,10 +2546,8 @@
           <t>11000029943</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>R$ 430,86</t>
-        </is>
+      <c r="E38" s="2" t="n">
+        <v>430.86</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2632,21 +2559,21 @@
           <t>2026-06-20 17:36:32 -03:00</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>thiago.sayao@gmail.com</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>thiago.sayao@gmail.com</t>
+          <t>tran_WRJqbYAseYTwLpmE</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>tran_WRJqbYAseYTwLpmE</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2671,10 +2598,8 @@
           <t>Q6O1I1LU95</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>R$ 313,40</t>
-        </is>
+      <c r="E39" s="2" t="n">
+        <v>313.4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2688,7 +2613,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4446498606</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2698,17 +2623,17 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4446498606</t>
+          <t>paulo.victorsn@gmail.com</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>paulo.victorsn@gmail.com</t>
+          <t>tran_0djM7JxSrSaAOREm</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>tran_0djM7JxSrSaAOREm</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2733,10 +2658,8 @@
           <t>JD1ZIZIY3P</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>R$ 408,50</t>
-        </is>
+      <c r="E40" s="2" t="n">
+        <v>408.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2750,7 +2673,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4446664204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2760,17 +2683,17 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4446664204</t>
+          <t>thatiane.nunes.pereira@gmail.com</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>thatiane.nunes.pereira@gmail.com</t>
+          <t>tran_jb9LMxBIdJIEBGXp</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>tran_jb9LMxBIdJIEBGXp</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2795,10 +2718,8 @@
           <t>L5EDB6HY5G</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>R$ 148,22</t>
-        </is>
+      <c r="E41" s="2" t="n">
+        <v>148.22</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2812,7 +2733,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4446721086</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2822,17 +2743,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4446721086</t>
+          <t>elianehiga@gmail.com</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>elianehiga@gmail.com</t>
+          <t>tran_LX7zjRb7fGs6jnA6</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>tran_LX7zjRb7fGs6jnA6</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2857,10 +2778,8 @@
           <t>DJ7R7AXFOJ</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>R$ 1.093,61</t>
-        </is>
+      <c r="E42" s="2" t="n">
+        <v>1093.61</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2874,7 +2793,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4447114682</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2884,17 +2803,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4447114682</t>
+          <t>mariliadfontes@gmail.com</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>mariliadfontes@gmail.com</t>
+          <t>tran_3DYzvrgTWMtvzmKp</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>tran_3DYzvrgTWMtvzmKp</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2919,10 +2838,8 @@
           <t>RL9VAK7IX2</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>R$ 520,50</t>
-        </is>
+      <c r="E43" s="2" t="n">
+        <v>520.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2936,7 +2853,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4447281406</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2946,17 +2863,17 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4447281406</t>
+          <t>helena.avzaradel@gmail.com</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>helena.avzaradel@gmail.com</t>
+          <t>tran_6Wdb1aDUds4Pq7gA</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>tran_6Wdb1aDUds4Pq7gA</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2981,10 +2898,8 @@
           <t>7YZFPRT34O</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>R$ 90,21</t>
-        </is>
+      <c r="E44" s="2" t="n">
+        <v>90.20999999999999</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2998,7 +2913,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4447374889</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3008,17 +2923,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4447374889</t>
+          <t>gisa.fernanda@terra.com.br</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>gisa.fernanda@terra.com.br</t>
+          <t>tran_Y293VmxEC2TvJvjQ</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>tran_Y293VmxEC2TvJvjQ</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3043,10 +2958,8 @@
           <t>11000029951</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>R$ 231,55</t>
-        </is>
+      <c r="E45" s="2" t="n">
+        <v>231.55</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3058,21 +2971,21 @@
           <t>2026-06-21 15:07:22 -03:00</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Rodrigo.santana12345@outlook.com</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Rodrigo.santana12345@outlook.com</t>
+          <t>tran_xrMA8OS2BIZ5jz4G</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>tran_xrMA8OS2BIZ5jz4G</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3097,10 +3010,8 @@
           <t>MZV2IP3IZO</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>R$ 169,98</t>
-        </is>
+      <c r="E46" s="2" t="n">
+        <v>169.98</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3114,7 +3025,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4447415412</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3124,17 +3035,17 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4447415412</t>
+          <t>marcia.posman@uol.com.br</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>marcia.posman@uol.com.br</t>
+          <t>tran_LDkpjMGS9bf9rEYR</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>tran_LDkpjMGS9bf9rEYR</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3159,10 +3070,8 @@
           <t>1Q4JTPUMKV</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>R$ 894,34</t>
-        </is>
+      <c r="E47" s="2" t="n">
+        <v>894.34</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3176,7 +3085,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4447538965</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3186,17 +3095,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4447538965</t>
+          <t>roselanhe@yahoo.com.br</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>roselanhe@yahoo.com.br</t>
+          <t>tran_E75Pe6AAfdhPLlR0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>tran_E75Pe6AAfdhPLlR0</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3221,10 +3130,8 @@
           <t>KOG6SZGH1W</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>R$ 1.297,95</t>
-        </is>
+      <c r="E48" s="2" t="n">
+        <v>1297.95</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3238,7 +3145,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4447611652</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3248,17 +3155,17 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4447611652</t>
+          <t>van_mek@hotmail.com</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>van_mek@hotmail.com</t>
+          <t>tran_mvwd0NATWcDGylXp</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>tran_mvwd0NATWcDGylXp</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3283,10 +3190,8 @@
           <t>2PWANKAOY4</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>R$ 223,40</t>
-        </is>
+      <c r="E49" s="2" t="n">
+        <v>223.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3300,7 +3205,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4447669667</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3310,17 +3215,17 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>4447669667</t>
+          <t>delainesoares@hotmail.com</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>delainesoares@hotmail.com</t>
+          <t>tran_VB4O8E6h8wu0bday</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>tran_VB4O8E6h8wu0bday</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3345,10 +3250,8 @@
           <t>11000029955</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>R$ 100,28</t>
-        </is>
+      <c r="E50" s="2" t="n">
+        <v>100.28</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3360,21 +3263,21 @@
           <t>2026-06-21 18:49:58 -03:00</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>mkataoka@gmail.com</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>mkataoka@gmail.com</t>
+          <t>tran_NyqzrPGlCdcvoaY8</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>tran_NyqzrPGlCdcvoaY8</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3399,10 +3302,8 @@
           <t>11000029956</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>R$ 408,91</t>
-        </is>
+      <c r="E51" s="2" t="n">
+        <v>408.91</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3414,21 +3315,21 @@
           <t>2026-06-21 18:51:15 -03:00</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>erich.augusto@hotmail.com</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>erich.augusto@hotmail.com</t>
+          <t>tran_8KrpV5NFEVHrDzwy</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>tran_8KrpV5NFEVHrDzwy</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3453,10 +3354,8 @@
           <t>JNW1UPNHV3</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>R$ 414,78</t>
-        </is>
+      <c r="E52" s="2" t="n">
+        <v>414.78</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3470,7 +3369,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4447712040</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3480,17 +3379,17 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4447712040</t>
+          <t>nessaaah_@hotmail.com</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>nessaaah_@hotmail.com</t>
+          <t>tran_gDMmDJSMZSa292XL</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>tran_gDMmDJSMZSa292XL</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3515,10 +3414,8 @@
           <t>11000029958</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>R$ 667,31</t>
-        </is>
+      <c r="E53" s="2" t="n">
+        <v>667.3099999999999</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3530,21 +3427,21 @@
           <t>2026-06-21 19:31:01 -03:00</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>felipeguimaraesusa@gmail.com</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>felipeguimaraesusa@gmail.com</t>
+          <t>tran_vOMzmJ8ibwS6xYl3</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>tran_vOMzmJ8ibwS6xYl3</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3569,10 +3466,8 @@
           <t>11000029959</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>R$ 386,11</t>
-        </is>
+      <c r="E54" s="2" t="n">
+        <v>386.11</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3584,21 +3479,21 @@
           <t>2026-06-21 19:33:29 -03:00</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>adrianamdvb@gmail.com</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>adrianamdvb@gmail.com</t>
+          <t>tran_Y0QK62AdTwHkj72l</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>tran_Y0QK62AdTwHkj72l</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3623,10 +3518,8 @@
           <t>LOVYU9YT1Q</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>R$ 271,60</t>
-        </is>
+      <c r="E55" s="2" t="n">
+        <v>271.6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3640,7 +3533,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>4447841994</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3650,22 +3543,74 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>4447841994</t>
+          <t>sufruzeri@gmail.com</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>sufruzeri@gmail.com</t>
+          <t>tran_VDY8G8PsmHvlGkg3</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>tran_VDY8G8PsmHvlGkg3</t>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Renata Andrade</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DVZF2LHN93</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>11000029961</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>276.25</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>pix</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-06-21 22:39:47 -03:00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>renata.andradefranco@gmail.com</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>tran_mXe548HOLsdx5RJb</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L55"/>
+  <autoFilter ref="A1:L56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3686,11 +3631,11 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3731,27 +3676,27 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>NSU</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TID</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Customer_Email</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction_Id</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>flag</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>NSU</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TID</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Customer_Email</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transaction_Id</t>
         </is>
       </c>
     </row>
@@ -3776,10 +3721,8 @@
           <t>11000029920</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>R$ 490,50</t>
-        </is>
+      <c r="E2" s="2" t="n">
+        <v>490.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3791,21 +3734,21 @@
           <t>2026-06-19 12:35:40 -03:00</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dond.22@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>tran_znR5KbwBs8CkZb8k</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>dond.22@hotmail.com</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>tran_znR5KbwBs8CkZb8k</t>
         </is>
       </c>
     </row>
@@ -3830,10 +3773,8 @@
           <t>11000029921</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>R$ 381,12</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>381.12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3845,21 +3786,21 @@
           <t>2026-06-19 12:52:51 -03:00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dond.22@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>tran_jgQWbmwGcyhwqLPO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>dond.22@hotmail.com</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>tran_jgQWbmwGcyhwqLPO</t>
         </is>
       </c>
     </row>

--- a/Projetos/Lojas Conamore/Relatórios Pagar.me/ACL/Pagarme_ACL_2026-06-19_21.xlsx
+++ b/Projetos/Lojas Conamore/Relatórios Pagar.me/ACL/Pagarme_ACL_2026-06-19_21.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Revisar" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Aprovados'!$A$1:$L$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Revisar'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Aprovados'!$A$1:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Revisar'!$A$1:$N$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,21 +430,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,55 +457,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Customer_Document</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>cliente</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pedido</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>referência</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meio</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>aprovado_em</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>NSU</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TID</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Customer_Email</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Charge_Id</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Transaction_Id</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
@@ -517,53 +529,63 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>37402073882</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Meguiane  Arruda</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>PM9FRDIY57</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>PM9FRDIY57</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" t="n">
         <v>339.88</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2026-06-19 00:27:10 -03:00</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>4444298196</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>4444298196</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>meggomesarruda@gmail.com</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ch_p9YWV4XsbIVvmk0r</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>tran_nwBk3x3Sph374RdA</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -577,53 +599,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>88738590204</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>JULIA LINHARES</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>ERVRBKZIW1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>ERVRBKZIW1</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" t="n">
         <v>913.2</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-19 02:09:30 -03:00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>4444338237</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>4444338237</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>juliaclinhares@yahoo.com.br</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ch_1EVGN6nIDLt3GMZ2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>tran_lyAvn4GH4TejKLjW</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -637,45 +669,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>40158681886</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Lara Império</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>837FLDI7O6</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>44000002474</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" t="n">
         <v>279.39</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>boleto</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2026-06-19 08:23:37 -03:00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>laraimperio28@gmail.com</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ch_ZQn17z5dIaFnrxgv</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>tran_NzPWYZnfjhOY07Xx</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -689,45 +731,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>02413717161</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>TATIELLY GARCEZ REVOREDO MARQUES</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>EL8ZH9HGDP</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>11000029912</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" t="n">
         <v>753.78</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2026-06-19 09:28:17 -03:00</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>tatiellyrevoredo@gmail.com</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ch_qMvYbyBkFYcAJPXB</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>tran_2vBrVyrauBTv0xq6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -741,53 +793,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>14015762819</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Andréa Hilário</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>3D2U0DI1N3</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>3D2U0DI1N3</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" t="n">
         <v>129.75</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2026-06-19 09:40:58 -03:00</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>4444555290</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>4444555290</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>andrea.hilario40@gmail.com</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ch_ZywAo9eFJsVoL4rO</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>tran_9rB0Q3pFAnc6kx5D</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -801,53 +863,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>08733412600</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Felipe Moyses</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>QZ5U7DCVVW</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>QZ5U7DCVVW</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" t="n">
         <v>977.4</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>2026-06-19 09:50:32 -03:00</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>4444567231</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>4444567231</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>luanrsilva@hotmail.com</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ch_gwYALPiRNfYzAPZo</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>tran_2PV4QNqSRKsmXd7D</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -861,53 +933,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>10169198758</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Tatiana Fonseca</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>PKKWH31CKP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>PKKWH31CKP</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" t="n">
         <v>962.16</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>2026-06-19 10:54:02 -03:00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>4444644503</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>4444644503</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>tatiff21@hotmail.com</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ch_39jax9HWjUxnqv76</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>tran_X7kK55Gie8cbKm5J</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -921,53 +1003,63 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>04743452112</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Lucas Abrantes</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>7E2JTR1CQL</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>7E2JTR1CQL</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" t="n">
         <v>697</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>2026-06-19 11:01:20 -03:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>4444653357</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>4444653357</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>lucasthads@gmail.com</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ch_JYDgOMcqOcMzwAK1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>tran_Yk1waWmSxrs7y0oM</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -981,45 +1073,55 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>02654808092</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Suelen Garcia Bastos</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>RW2KHEGF94</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>11000029917</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" t="n">
         <v>734.38</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2026-06-19 11:44:25 -03:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>suelen.bastos@sjp.pr.gov.br</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ch_8Bz0LERTDAUJwGL2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>tran_nP1907asbUve3LBp</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1033,53 +1135,63 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>02187813851</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>marice conde</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>0K2XAVBR7Y</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>0K2XAVBR7Y</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" t="n">
         <v>731.2</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>2026-06-19 11:45:44 -03:00</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>4444707109</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>4444707109</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mariceconde@gmail.com</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ch_NpwnWvyswkfo587v</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>tran_P8yX4Vwi1H7Pj9vN</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1093,53 +1205,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>17390279737</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Gabriela Koehler Carvalho</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>W4NC46BLK2</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>W4NC46BLK2</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" t="n">
         <v>342.2</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2026-06-19 12:34:12 -03:00</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>4444766990</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>4444766990</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>gabickoehler@gmail.com</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ch_53AlPDYFQHyG6Zed</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>tran_8M4el9Mf0U5VrqAb</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1153,45 +1275,55 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>06371921843</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>erica moreira</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>7YOJSVRI8X</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>11000029920</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" t="n">
         <v>490.5</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>2026-06-19 12:35:40 -03:00</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>dond.22@hotmail.com</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ch_69bg5AbXF8Ux43pz</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>tran_znR5KbwBs8CkZb8k</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -1205,45 +1337,55 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>06371921843</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>erica moreira</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>J0O2S1PALK</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>11000029921</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" t="n">
         <v>381.12</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>2026-06-19 12:52:51 -03:00</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>dond.22@hotmail.com</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ch_jxNvx8JHofwOvqma</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>tran_jgQWbmwGcyhwqLPO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -1257,53 +1399,63 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>41540496821</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Nathalia Ricardo</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>E2OPS0AG0M</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>E2OPS0AG0M</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" t="n">
         <v>283.56</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2026-06-19 13:29:00 -03:00</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>4444833010</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>4444833010</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>nathalia.ricardo@live.com</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ch_lepKRb2F3LtWgK2P</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>tran_Omyw7Jxhvso3QJj0</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1317,45 +1469,55 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>14524381708</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>MAYRA HONORATO</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>VZ5OCGTK8E</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>44000002480</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="F16" t="n">
         <v>230.66</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>2026-06-19 15:12:23 -03:00</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>honoratoc.mayra@gmail.com</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ch_gVxKJ59IagUJyLzA</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>tran_MY9Jey9hryUpxJgW</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1369,53 +1531,63 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>20061522899</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>JULIANA TEIXEIRA BOMBIG</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>09RGUGEHVG</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>09RGUGEHVG</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" t="n">
         <v>372.1</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>2026-06-19 15:56:43 -03:00</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>4445009326</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>4445009326</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>julianabombig@gmail.com</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ch_k9EBp2NCWWcJGw4K</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>tran_adM9pWVspfKkeAOr</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1429,53 +1601,63 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>32014650896</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Rodrigo de Moura Lavoura</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>R9DMFLZTYZ</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>R9DMFLZTYZ</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="F18" t="n">
         <v>530.15</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>2026-06-19 15:58:54 -03:00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>4445011850</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>4445011850</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>bmoura975@gmail.com</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ch_aD6rXDMSwHpQz901</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>tran_vpkb5NCJBUllMWqm</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1489,45 +1671,55 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>31309374805</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Sandra Schnyder</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>PYQ9B21TM6</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>11000029924</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="F19" t="n">
         <v>598.3</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2026-06-19 16:19:36 -03:00</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>nenisdomosi@hotmail.com</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ch_qrxz5GkH9tge5v3X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>tran_EZzXdmeSrUbDJ2r8</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1541,45 +1733,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>01656606607</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Adrienne Viti</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>K19RTXIGW3</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>11000029925</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" t="n">
         <v>251.33</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>2026-06-19 16:51:12 -03:00</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>adrienneviti@gmail.com</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ch_0vRmr7EHxCa4lKod</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>tran_DKbV8drTkJIRVJmM</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1593,45 +1795,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>09708789828</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Milene Dumont</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>XWZ5A7YI97</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>44000002482</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="F21" t="n">
         <v>154.67</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>2026-06-19 17:19:35 -03:00</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
         <is>
           <t>mi.dumont2009@gmail.com</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>ch_JrnO0pGFLs9vlXaL</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>tran_MADx3L2i2MIDLb0g</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1645,45 +1857,55 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>86282042704</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>SEBASTIÃO GERALDO DA SILVA BRITO</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>P9LDTYNAKJ</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>11000029926</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="F22" t="n">
         <v>511.7</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>2026-06-19 17:31:50 -03:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>shoah7779@gmail.com</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ch_EZA92eGXFXFXj1Wy</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>tran_aKZrzPO0uyIXWGJV</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1697,53 +1919,63 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>08676688818</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Loana Maria de Siqueira</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>7K05XSDS4P</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>7K05XSDS4P</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="F23" t="n">
         <v>1172</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>2026-06-19 21:05:57 -03:00</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>4445470737</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>4445470737</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>lomasiq@gmail.com</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ch_vkBOV8etXc8pwg4E</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>tran_xEabz9VIGduX6r39</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1757,53 +1989,63 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>06008888600</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Alessandra Moura</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>QM6OSL4B2Z</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>QM6OSL4B2Z</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="F24" t="n">
         <v>585.48</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>2026-06-19 22:39:22 -03:00</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>4445562066</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>4445562066</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>dellep24@hotmail.com</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>ch_6nzNd8RfA9HqNEw4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>tran_MQrzq7RtOYSxYDdj</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1817,53 +2059,63 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>44071876034</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Berenice Nunes</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>6M4GWU5SQ8</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>6M4GWU5SQ8</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="F25" t="n">
         <v>395.6</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>2026-06-20 08:46:19 -03:00</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>4445821974</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>4445821974</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>bere_martez@outlook.com</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>ch_RAx8QjRTxVIaQ41q</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>tran_e360g0kHmMi3R7qx</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1877,53 +2129,63 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>36135033875</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Deborah Maeda</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>04E3CWF928</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>04E3CWF928</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="F26" t="n">
         <v>157.51</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>2026-06-20 09:10:06 -03:00</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>4445844291</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>4445844291</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>dehfunchal@gmail.com</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ch_A7wr0qKu9iM3JZLX</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>tran_m3wMJDJCeeh08Wob</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1937,45 +2199,55 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>26168347828</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Angelina Villani Passarella</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>5O51TYJTEW</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>11000029931</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="F27" t="n">
         <v>176.33</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>2026-06-20 09:27:42 -03:00</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
         <is>
           <t>apassarella@hotmail.com</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ch_KA6zDOLIMSr5xO82</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>tran_y9W2MeDI5s6r0eqQ</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1989,45 +2261,55 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>34145827830</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>VANUSA Nascimento de melo</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>8XZ9TY1ULP</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>44000002483</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="F28" t="n">
         <v>224.2</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>2026-06-20 11:19:55 -03:00</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
         <is>
           <t>vanusa1melo@gmail.com</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>ch_NLV4x3NeFAUq6q7y</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>tran_wyg51p8IMf1KdoaX</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2041,45 +2323,55 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>10273225731</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>Eridan Roberto de Santana</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>EL1MHJMIVW</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>44000002484</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="F29" t="n">
         <v>262.86</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2026-06-20 13:22:23 -03:00</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
         <is>
           <t>eridanrobertos@gmail.com</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ch_r6Zb047cDrFnbBKW</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>tran_BYy9MXt7VfvBjZ4Q</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2093,45 +2385,55 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>78207762187</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Davidson Pereira de Souza Afonso Pinto</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>40Z5AKGAJ4</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>11000029932</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="F30" t="n">
         <v>338.88</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2026-06-20 14:05:39 -03:00</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
         <is>
           <t>filhodedavi.ms@gmail.com</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ch_K5OLWZrHluPwWZ6y</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>tran_Dyg68Q5FGvHVXPQA</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2145,53 +2447,63 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>13103499671</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>Ana Ponchon</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>6O8OA12SRK</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>6O8OA12SRK</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="F31" t="n">
         <v>511.18</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>2026-06-20 14:44:48 -03:00</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>4446212119</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>4446212119</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>acponchon@gmail.com</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>ch_6oeQGvYFauLazPR2</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>tran_m0PZbq1U4S0gb1yp</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2205,45 +2517,55 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>85235342372</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>José  Cavalcante Júnior</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>91DYC2WTX5</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>11000029935</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="F32" t="n">
         <v>344.44</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2026-06-20 15:17:26 -03:00</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
         <is>
           <t>cavalcantejuniorpi@yahoo.com.br</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>ch_w3B2rdgslzCKqOq4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>tran_7r9objAcW5hjwodZ</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2257,45 +2579,55 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>07286695797</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>Alessandra  Semm</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>P9QSX5H85P</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>11000029936</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="F33" t="n">
         <v>174.49</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>2026-06-20 15:31:11 -03:00</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
         <is>
           <t>portelalessandra@gmail.com</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ch_NQLJM4BcDKtGk6xG</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>tran_yrv3PNZc5mt4bKNq</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2309,45 +2641,55 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>02068715031</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Luiza Crochemore</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>N909HY6B8G</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>11000029938</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="F34" t="n">
         <v>1136.06</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>2026-06-20 16:17:28 -03:00</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
         <is>
           <t>crochemorelu@gmail.com</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ch_Z5VOPnNMS1t8P0mD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>tran_nkRE7ADUyhmY3rJY</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2361,45 +2703,55 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>90849450691</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>Andre Vinicius lino Silva  Pinto</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>XJJRAZJU06</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>11000029940</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="F35" t="n">
         <v>264.52</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>2026-06-20 16:56:43 -03:00</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
         <is>
           <t>andrepinto@indanet.com.br</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>ch_xM51xMgF4NFMOVke</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>tran_OP9QzkuEYcjRgVDw</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2413,53 +2765,63 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>76720187872</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Liane Henriques Fraccaroli</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>P69QB6CEKP</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>P69QB6CEKP</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="F36" t="n">
         <v>1457.4</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>2026-06-20 17:01:55 -03:00</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>4446359095</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>4446359095</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>liane@o2filmes.com</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>ch_6w5WLraAIqFrDKQO</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>tran_PqQKq30uyHVlDnZR</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2473,53 +2835,63 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>11693652641</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>Ananda  Lima</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>LK17C24U2E</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>LK17C24U2E</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="F37" t="n">
         <v>1546.3</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>2026-06-20 17:05:07 -03:00</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>4446362528</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>4446362528</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>doutoraanandalima@gmail.com</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>ch_o6wZN5J1IRF3nOyv</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>tran_ZaQrp6lhv7Sp9BzJ</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2533,45 +2905,55 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>04490526997</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Thiago Sayão</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>6KNOC9KBE6</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>11000029943</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="F38" t="n">
         <v>430.86</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>2026-06-20 17:36:32 -03:00</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
         <is>
           <t>thiago.sayao@gmail.com</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ch_xWYlPwWi5dckPD1g</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>tran_WRJqbYAseYTwLpmE</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2585,53 +2967,63 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>35069346865</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>Paulo Nogueira</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Q6O1I1LU95</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Q6O1I1LU95</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="F39" t="n">
         <v>313.4</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>2026-06-20 18:55:28 -03:00</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>4446498606</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>4446498606</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>paulo.victorsn@gmail.com</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>ch_lzwYJ5Ls5MfwoZ4Q</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>tran_0djM7JxSrSaAOREm</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2645,53 +3037,63 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>42434047807</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Thatiane Nunes</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>JD1ZIZIY3P</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>JD1ZIZIY3P</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="F40" t="n">
         <v>408.5</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>2026-06-20 21:23:22 -03:00</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>4446664204</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>4446664204</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>thatiane.nunes.pereira@gmail.com</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>ch_7BkVJvZsBU74J9q6</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>tran_jb9LMxBIdJIEBGXp</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2705,53 +3107,63 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>15195292876</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>Eliane Higa</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>L5EDB6HY5G</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>L5EDB6HY5G</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="F41" t="n">
         <v>148.22</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>2026-06-20 22:29:35 -03:00</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>4446721086</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>4446721086</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>elianehiga@gmail.com</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ch_WwRnR1YUeAiKlzKv</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>tran_LX7zjRb7fGs6jnA6</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2765,53 +3177,63 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>34631193824</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>Marilia Fontes</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>DJ7R7AXFOJ</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>DJ7R7AXFOJ</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="F42" t="n">
         <v>1093.61</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>2026-06-21 11:00:59 -03:00</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>4447114682</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>4447114682</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>mariliadfontes@gmail.com</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ch_8XjlErycwsaeorRa</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>tran_3DYzvrgTWMtvzmKp</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2825,53 +3247,63 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>06990950773</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>Helena Avzaradel</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>RL9VAK7IX2</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>RL9VAK7IX2</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="F43" t="n">
         <v>520.5</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>2026-06-21 13:17:42 -03:00</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>4447281406</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>4447281406</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>helena.avzaradel@gmail.com</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>ch_2zB4K7f6XCpE4DPW</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>tran_6Wdb1aDUds4Pq7gA</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2885,53 +3317,63 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>40572200897</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>Benedito mauro dos santos</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>7YZFPRT34O</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>7YZFPRT34O</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="F44" t="n">
         <v>90.20999999999999</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>2026-06-21 14:33:54 -03:00</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>4447374889</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>4447374889</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>gisa.fernanda@terra.com.br</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>ch_a3eBA00SZHdX5obw</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>tran_Y293VmxEC2TvJvjQ</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2945,45 +3387,55 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>15893801776</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>Rodrigo Santana</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>PJJ1H30AX1</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>11000029951</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="F45" t="n">
         <v>231.55</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>2026-06-21 15:07:22 -03:00</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Rodrigo.santana12345@outlook.com</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>ch_ZVlJVycMQFBeq2ND</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>tran_xrMA8OS2BIZ5jz4G</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2997,53 +3449,63 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>08578464850</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>Marcia  Posman</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>MZV2IP3IZO</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>MZV2IP3IZO</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="F46" t="n">
         <v>169.98</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>2026-06-21 15:07:56 -03:00</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>4447415412</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>4447415412</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>marcia.posman@uol.com.br</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>ch_5AnZbros4PiR1ZxV</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>tran_LDkpjMGS9bf9rEYR</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3057,53 +3519,63 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>01019737484</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Roselanhe Oliveira</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>1Q4JTPUMKV</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1Q4JTPUMKV</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="F47" t="n">
         <v>894.34</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>2026-06-21 16:57:29 -03:00</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>4447538965</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>4447538965</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>roselanhe@yahoo.com.br</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ch_K17vQAxsNQU9bvY6</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>tran_E75Pe6AAfdhPLlR0</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3117,53 +3589,63 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>30631258817</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>Vanessa Mekaru</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>KOG6SZGH1W</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>KOG6SZGH1W</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="F48" t="n">
         <v>1297.95</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>2026-06-21 17:59:44 -03:00</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>4447611652</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>4447611652</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>van_mek@hotmail.com</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>ch_ZOj81MFRMigQ8y0A</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>tran_mvwd0NATWcDGylXp</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3177,53 +3659,63 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>33767600803</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>Diego   dos Santos</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2PWANKAOY4</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>2PWANKAOY4</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="F49" t="n">
         <v>223.4</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>2026-06-21 18:40:56 -03:00</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>4447669667</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>4447669667</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>delainesoares@hotmail.com</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>ch_e1oVRn83fOIK4EQa</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>tran_VB4O8E6h8wu0bday</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3237,45 +3729,55 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>25543728883</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Marcio Kataoka</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>43Z51B6SKL</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>11000029955</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="F50" t="n">
         <v>100.28</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>2026-06-21 18:49:58 -03:00</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
         <is>
           <t>mkataoka@gmail.com</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>ch_jAQJynsQkF73ByYL</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>tran_NyqzrPGlCdcvoaY8</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3289,45 +3791,55 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>00904603911</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>Erich Augusto  Grunevald</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>9MN6C1VB3K</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>11000029956</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="F51" t="n">
         <v>408.91</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>2026-06-21 18:51:15 -03:00</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
         <is>
           <t>erich.augusto@hotmail.com</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>ch_rKEnvEwkh6SKJ1Vm</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>tran_8KrpV5NFEVHrDzwy</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3341,53 +3853,63 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>06979397907</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>Vanessa Schroeder</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>JNW1UPNHV3</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>JNW1UPNHV3</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="F52" t="n">
         <v>414.78</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>2026-06-21 19:11:00 -03:00</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>4447712040</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>4447712040</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>nessaaah_@hotmail.com</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>ch_KnbQnR1upKtePQoV</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>tran_gDMmDJSMZSa292XL</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3401,45 +3923,55 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>14407011645</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>Felipe Guimarães Figueiredo de Oliveira Motta</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>L41SWYTQ1L</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>11000029958</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="F53" t="n">
         <v>667.3099999999999</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>2026-06-21 19:31:01 -03:00</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
         <is>
           <t>felipeguimaraesusa@gmail.com</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>ch_Nrmbkp36hotldw6E</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>tran_vOMzmJ8ibwS6xYl3</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3453,45 +3985,55 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>06014598000154</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>Campolina Diniz investimentos ltda</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>6Q32T8QIE1</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>11000029959</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="F54" t="n">
         <v>386.11</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>2026-06-21 19:33:29 -03:00</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
         <is>
           <t>adrianamdvb@gmail.com</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ch_Y38vlmkHkC7WZpRD</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>tran_Y0QK62AdTwHkj72l</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3505,53 +4047,63 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>05134737932</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Suelem Larissa  Fruzeri Desiro</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>LOVYU9YT1Q</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>LOVYU9YT1Q</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="F55" t="n">
         <v>271.6</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>credit_card</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>2026-06-21 21:02:10 -03:00</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>4447841994</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>4447841994</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>sufruzeri@gmail.com</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>ch_OxP2zPSwpUjMByma</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t>tran_VDY8G8PsmHvlGkg3</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3565,52 +4117,62 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>43128962839</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>Renata Andrade</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>DVZF2LHN93</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>11000029961</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="F56" t="n">
         <v>276.25</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>2026-06-21 22:39:47 -03:00</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
         <is>
           <t>renata.andradefranco@gmail.com</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>ch_8PypoKDFztvqXVdG</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>tran_mXe548HOLsdx5RJb</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L56"/>
+  <autoFilter ref="A1:N56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3621,21 +4183,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3646,55 +4210,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Customer_Document</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>cliente</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pedido</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>referência</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meio</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>aprovado_em</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>NSU</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TID</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Customer_Email</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Charge_Id</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Transaction_Id</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
@@ -3708,45 +4282,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>06371921843</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>erica moreira</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>7YOJSVRI8X</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>11000029920</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" t="n">
         <v>490.5</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2026-06-19 12:35:40 -03:00</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>dond.22@hotmail.com</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ch_69bg5AbXF8Ux43pz</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>tran_znR5KbwBs8CkZb8k</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -3760,52 +4344,62 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>06371921843</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>erica moreira</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>J0O2S1PALK</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>11000029921</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" t="n">
         <v>381.12</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>pix</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-19 12:52:51 -03:00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>dond.22@hotmail.com</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ch_jxNvx8JHofwOvqma</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>tran_jgQWbmwGcyhwqLPO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>